--- a/docs/2627/report/dapr3_2627_report_rubric.xlsx
+++ b/docs/2627/report/dapr3_2627_report_rubric.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jking34\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jking34\Desktop\uoepsy_courses\dapr3\docs\2627\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2707E7-D41F-46FB-971A-204027D2B139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F90261-3C3E-458E-9EAC-6C7725B7541A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{80E36928-E358-2446-BA2E-DC98679EB28E}"/>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6478FE4C-0DDA-3A4B-B07C-63BB646B301E}"/>
+    <workbookView minimized="1" xWindow="-25485" yWindow="-1110" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{80E36928-E358-2446-BA2E-DC98679EB28E}"/>
+    <workbookView xWindow="-28920" yWindow="-2805" windowWidth="29040" windowHeight="15720" xr2:uid="{6478FE4C-0DDA-3A4B-B07C-63BB646B301E}"/>
   </bookViews>
   <sheets>
     <sheet name="RUBRIC" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="82">
   <si>
     <t>Category</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Analysis decisions</t>
   </si>
   <si>
-    <t>You tidy the data appropriately.</t>
-  </si>
-  <si>
     <t>All your contrast coding/transformation decisions are appropriate for your analysis goals.</t>
   </si>
   <si>
@@ -88,24 +85,15 @@
     <t>Describing analysis</t>
   </si>
   <si>
-    <t>You clearly describe the process of maximal model building and potentially simplification that led to the model you fit.</t>
-  </si>
-  <si>
     <t>Describing results</t>
   </si>
   <si>
-    <t>You clearly report appropriate descriptive statistics.</t>
-  </si>
-  <si>
     <t>All figures and tables give your reader useful information about your data/analysis.</t>
   </si>
   <si>
     <t>For each relevant estimated quantity, you describe what it means and report its inferential information (e.g., test statistic, CI, and p-value).</t>
   </si>
   <si>
-    <t>You visualise the model's fitted estimates in a single figure.</t>
-  </si>
-  <si>
     <t>You clearly and concisely report your model assumption/diagnostic checks (including plots in an appendix, if desired).</t>
   </si>
   <si>
@@ -271,20 +259,17 @@
     <t>yep</t>
   </si>
   <si>
-    <t>feedback</t>
-  </si>
-  <si>
     <t>You fit a model that reasonably represents the data generating process.</t>
   </si>
   <si>
-    <t>You accurately, thoroughly, and concisely describe the steps you took to tidy the data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You accurately, thoroughly, and concisely describe and motivate your contrast coding/transformation decisions. </t>
+    <t>You accurately and concisely describe the steps you took to tidy the data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You accurately and concisely describe and motivate your contrast coding/transformation decisions. </t>
   </si>
   <si>
     <r>
-      <t>You accurately, thoroughly, and concisely describe your chosen model.</t>
+      <t>You accurately and concisely describe your chosen model.</t>
     </r>
     <r>
       <rPr>
@@ -296,12 +281,30 @@
       <t xml:space="preserve"> </t>
     </r>
   </si>
+  <si>
+    <t>You clearly describe the process of maximal model building and simplification (if any) that led to the model you fit.</t>
+  </si>
+  <si>
+    <t>You clearly describe the sample and report appropriate descriptive statistics</t>
+  </si>
+  <si>
+    <t>For each relevant estimated quantity, you describe what it means and report its inferential information (e.g., test statistic, CI or test statistic, df (where appropriate) and p-value).</t>
+  </si>
+  <si>
+    <t>You visualise your key results</t>
+  </si>
+  <si>
+    <t>You introduce each figure and table in the text and cross-reference their numbers appropriately (including figures shown in the Appendix).</t>
+  </si>
+  <si>
+    <t>You accurately interpret the estimated quantity(ies) from your analysis to address the RQ(s)/hypothesis(es).</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -448,7 +451,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1"/>
@@ -476,17 +479,20 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="2" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="2" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -836,20 +842,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38D9F8AD-D668-7A48-9621-5844165D3017}">
-  <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:O21"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.21875" customWidth="1"/>
-    <col min="2" max="2" width="50.6640625" customWidth="1"/>
-    <col min="3" max="3" width="44.77734375" customWidth="1"/>
-    <col min="4" max="4" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.77734375" customWidth="1"/>
-    <col min="9" max="9" width="2.44140625" customWidth="1"/>
+    <col min="1" max="1" width="19.25" customWidth="1"/>
+    <col min="2" max="2" width="50.625" customWidth="1"/>
+    <col min="3" max="3" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.75" customWidth="1"/>
+    <col min="8" max="8" width="2.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="8" customFormat="1" ht="47.25">
+    <row r="1" spans="1:15" s="8" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -857,473 +862,438 @@
         <v>1</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7" t="s">
+      <c r="H1" s="7"/>
+      <c r="I1" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15">
+    <row r="2" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="24" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="19"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="21" t="str">
-        <f>IF(COUNT(D2,E2,F2,G2)=2, "More than one entry!", IF(COUNT(D2,E2,F2,G2)=0, "No entries!", ""))</f>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="20" t="str">
+        <f t="shared" ref="G2:G21" si="0">IF(COUNT(C2,D2,E2,F2)=2, "More than one entry!", IF(COUNT(C2,D2,E2,F2)=0, "No entries!", ""))</f>
         <v>No entries!</v>
       </c>
-      <c r="J2" s="4">
-        <f>IF($D2=1, 3, IF($E2=1, 2, IF($F2=1, 1, IF($G2 = 1, 0, 0))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15">
+      <c r="I2" s="4">
+        <f>IF($C2=1, 3, IF($D2=1, 2, IF($E2=1, 1, IF($F2 = 1, 0, 0))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="24" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="19"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="21" t="str">
-        <f>IF(COUNT(D3,E3,F3,G3)=2, "More than one entry!", IF(COUNT(D3,E3,F3,G3)=0, "No entries!", ""))</f>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="20" t="str">
+        <f t="shared" si="0"/>
         <v>No entries!</v>
       </c>
-      <c r="J3" s="4">
-        <f>IF($D3=1, 3, IF($E3=1, 2, IF($F3=1, 1, IF($G3 = 1, 0, 0))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15">
+      <c r="I3" s="4">
+        <f>IF($C3=1, 3, IF($D3=1, 2, IF($E3=1, 1, IF($F3 = 1, 0, 0))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="26" t="s">
-        <v>11</v>
+      <c r="B4" s="24" t="s">
+        <v>72</v>
       </c>
       <c r="C4" s="19"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="21" t="str">
-        <f>IF(COUNT(D4,E4,F4,G4)=2, "More than one entry!", IF(COUNT(D4,E4,F4,G4)=0, "No entries!", ""))</f>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="20" t="str">
+        <f t="shared" si="0"/>
         <v>No entries!</v>
       </c>
-      <c r="J4" s="4">
-        <f>IF($D4=1, 3, IF($E4=1, 2, IF($F4=1, 1, IF($G4 = 1, 0, 0))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15">
+      <c r="I4" s="4">
+        <f>IF($C4=1, 3, IF($D4=1, 2, IF($E4=1, 1, IF($F4 = 1, 0, 0))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="26" t="s">
-        <v>77</v>
+      <c r="B5" s="24" t="s">
+        <v>12</v>
       </c>
       <c r="C5" s="19"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="21" t="str">
-        <f>IF(COUNT(D5,E5,F5,G5)=2, "More than one entry!", IF(COUNT(D5,E5,F5,G5)=0, "No entries!", ""))</f>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="20" t="str">
+        <f t="shared" si="0"/>
         <v>No entries!</v>
       </c>
-      <c r="J5" s="4">
-        <f>IF($D5=1, 3, IF($E5=1, 2, IF($F5=1, 1, IF($G5 = 1, 0, 0))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="30">
-      <c r="A6" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="26" t="s">
+      <c r="I5" s="4">
+        <f>IF($C5=1, 3, IF($D5=1, 2, IF($E5=1, 1, IF($F5 = 1, 0, 0))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
         <v>13</v>
       </c>
+      <c r="B6" s="25" t="s">
+        <v>73</v>
+      </c>
       <c r="C6" s="19"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="21" t="str">
-        <f>IF(COUNT(D6,E6,F6,G6)=2, "More than one entry!", IF(COUNT(D6,E6,F6,G6)=0, "No entries!", ""))</f>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="20" t="str">
+        <f t="shared" si="0"/>
         <v>No entries!</v>
       </c>
-      <c r="J6" s="4">
-        <f>IF($D6=1, 3, IF($E6=1, 2, IF($F6=1, 1, IF($G6 = 1, 0, 0))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15">
-      <c r="A7" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="21" t="str">
-        <f>IF(COUNT(D7,E7,F7,G7)=2, "More than one entry!", IF(COUNT(D7,E7,F7,G7)=0, "No entries!", ""))</f>
+      <c r="I6" s="4">
+        <f>IF($C6=1, 3, IF($D6=1, 2, IF($E6=1, 1, IF($F6 = 1, 0, 0))))</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="26"/>
+    </row>
+    <row r="7" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="20" t="str">
+        <f t="shared" si="0"/>
         <v>No entries!</v>
       </c>
-      <c r="J7" s="4">
-        <f>IF($D7=1, 3, IF($E7=1, 2, IF($F7=1, 1, IF($G7 = 1, 0, 0))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="30">
-      <c r="A8" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="23"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="21" t="str">
-        <f>IF(COUNT(D8,E8,F8,G8)=2, "More than one entry!", IF(COUNT(D8,E8,F8,G8)=0, "No entries!", ""))</f>
+      <c r="I7" s="4">
+        <f>IF($C7=1, 3, IF($D7=1, 2, IF($E7=1, 1, IF($F7 = 1, 0, 0))))</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="26"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="28"/>
+    </row>
+    <row r="8" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="20" t="str">
+        <f t="shared" si="0"/>
         <v>No entries!</v>
       </c>
-      <c r="J8" s="4">
-        <f>IF($D8=1, 3, IF($E8=1, 2, IF($F8=1, 1, IF($G8 = 1, 0, 0))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="30">
-      <c r="A9" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>15</v>
+      <c r="I8" s="4">
+        <f>IF($C8=1, 3, IF($D8=1, 2, IF($E8=1, 1, IF($F8 = 1, 0, 0))))</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>75</v>
       </c>
       <c r="C9" s="19"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21" t="str">
-        <f>IF(COUNT(D9,E9,F9,G9)=2, "More than one entry!", IF(COUNT(D9,E9,F9,G9)=0, "No entries!", ""))</f>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="20" t="str">
+        <f t="shared" si="0"/>
         <v>No entries!</v>
       </c>
-      <c r="J9" s="4">
-        <f>IF($D9=1, 3, IF($E9=1, 2, IF($F9=1, 1, IF($G9 = 1, 0, 0))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15">
+      <c r="I9" s="4">
+        <f>IF($C9=1, 3, IF($D9=1, 2, IF($E9=1, 1, IF($F9 = 1, 0, 0))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>No entries!</v>
+      </c>
+      <c r="I10" s="4">
+        <f>IF($C10=1, 3, IF($D10=1, 2, IF($E10=1, 1, IF($F10 = 1, 0, 0))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>No entries!</v>
+      </c>
+      <c r="I11" s="4">
+        <f>IF($C11=1, 3, IF($D11=1, 2, IF($E11=1, 1, IF($F11 = 1, 0, 0))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="63" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>No entries!</v>
+      </c>
+      <c r="I12" s="4">
+        <f>IF($C12=1, 3, IF($D12=1, 2, IF($E12=1, 1, IF($F12 = 1, 0, 0))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>No entries!</v>
+      </c>
+      <c r="I13" s="4">
+        <f>IF($C13=1, 3, IF($D13=1, 2, IF($E13=1, 1, IF($F13 = 1, 0, 0))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>No entries!</v>
+      </c>
+      <c r="I14" s="4">
+        <f>IF($C14=1, 3, IF($D14=1, 2, IF($E14=1, 1, IF($F14 = 1, 0, 0))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>No entries!</v>
+      </c>
+      <c r="I15" s="4">
+        <f>IF($C15=1, 3, IF($D15=1, 2, IF($E15=1, 1, IF($F15 = 1, 0, 0))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>No entries!</v>
+      </c>
+      <c r="I16" s="4">
+        <f>IF($C16=1, 3, IF($D16=1, 2, IF($E16=1, 1, IF($F16 = 1, 0, 0))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>No entries!</v>
+      </c>
+      <c r="I17" s="4">
+        <f>IF($C17=1, 3, IF($D17=1, 2, IF($E17=1, 1, IF($F17 = 1, 0, 0))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>No entries!</v>
+      </c>
+      <c r="I18" s="4">
+        <f>IF($C18=1, 3, IF($D18=1, 2, IF($E18=1, 1, IF($F18 = 1, 0, 0))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="21" t="str">
-        <f>IF(COUNT(D10,E10,F10,G10)=2, "More than one entry!", IF(COUNT(D10,E10,F10,G10)=0, "No entries!", ""))</f>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="20" t="str">
+        <f t="shared" si="0"/>
         <v>No entries!</v>
       </c>
-      <c r="J10" s="4">
-        <f>IF($D10=1, 3, IF($E10=1, 2, IF($F10=1, 1, IF($G10 = 1, 0, 0))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="15">
-      <c r="A11" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="21" t="str">
-        <f>IF(COUNT(D11,E11,F11,G11)=2, "More than one entry!", IF(COUNT(D11,E11,F11,G11)=0, "No entries!", ""))</f>
+      <c r="I19" s="4">
+        <f>IF($C19=1, 3, IF($D19=1, 2, IF($E19=1, 1, IF($F19 = 1, 0, 0))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="20" t="str">
+        <f t="shared" si="0"/>
         <v>No entries!</v>
       </c>
-      <c r="J11" s="4">
-        <f>IF($D11=1, 3, IF($E11=1, 2, IF($F11=1, 1, IF($G11 = 1, 0, 0))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="15">
-      <c r="A12" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="21" t="str">
-        <f>IF(COUNT(D12,E12,F12,G12)=2, "More than one entry!", IF(COUNT(D12,E12,F12,G12)=0, "No entries!", ""))</f>
+      <c r="I20" s="4">
+        <f>IF($C20=1, 3, IF($D20=1, 2, IF($E20=1, 1, IF($F20 = 1, 0, 0))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="20" t="str">
+        <f t="shared" si="0"/>
         <v>No entries!</v>
       </c>
-      <c r="J12" s="4">
-        <f>IF($D12=1, 3, IF($E12=1, 2, IF($F12=1, 1, IF($G12 = 1, 0, 0))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="30">
-      <c r="A13" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="21" t="str">
-        <f>IF(COUNT(D13,E13,F13,G13)=2, "More than one entry!", IF(COUNT(D13,E13,F13,G13)=0, "No entries!", ""))</f>
-        <v>No entries!</v>
-      </c>
-      <c r="J13" s="4">
-        <f>IF($D13=1, 3, IF($E13=1, 2, IF($F13=1, 1, IF($G13 = 1, 0, 0))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="15">
-      <c r="A14" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="21" t="str">
-        <f>IF(COUNT(D14,E14,F14,G14)=2, "More than one entry!", IF(COUNT(D14,E14,F14,G14)=0, "No entries!", ""))</f>
-        <v>No entries!</v>
-      </c>
-      <c r="J14" s="4">
-        <f>IF($D14=1, 3, IF($E14=1, 2, IF($F14=1, 1, IF($G14 = 1, 0, 0))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="30">
-      <c r="A15" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="21" t="str">
-        <f>IF(COUNT(D15,E15,F15,G15)=2, "More than one entry!", IF(COUNT(D15,E15,F15,G15)=0, "No entries!", ""))</f>
-        <v>No entries!</v>
-      </c>
-      <c r="J15" s="4">
-        <f>IF($D15=1, 3, IF($E15=1, 2, IF($F15=1, 1, IF($G15 = 1, 0, 0))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="15">
-      <c r="A16" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="21" t="str">
-        <f>IF(COUNT(D16,E16,F16,G16)=2, "More than one entry!", IF(COUNT(D16,E16,F16,G16)=0, "No entries!", ""))</f>
-        <v>No entries!</v>
-      </c>
-      <c r="J16" s="4">
-        <f>IF($D16=1, 3, IF($E16=1, 2, IF($F16=1, 1, IF($G16 = 1, 0, 0))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="21" t="str">
-        <f>IF(COUNT(D17,E17,F17,G17)=2, "More than one entry!", IF(COUNT(D17,E17,F17,G17)=0, "No entries!", ""))</f>
-        <v>No entries!</v>
-      </c>
-      <c r="J17" s="4">
-        <f>IF($D17=1, 3, IF($E17=1, 2, IF($F17=1, 1, IF($G17 = 1, 0, 0))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="30">
-      <c r="A18" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="21" t="str">
-        <f>IF(COUNT(D18,E18,F18,G18)=2, "More than one entry!", IF(COUNT(D18,E18,F18,G18)=0, "No entries!", ""))</f>
-        <v>No entries!</v>
-      </c>
-      <c r="J18" s="4">
-        <f>IF($D18=1, 3, IF($E18=1, 2, IF($F18=1, 1, IF($G18 = 1, 0, 0))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="21" t="str">
-        <f>IF(COUNT(D19,E19,F19,G19)=2, "More than one entry!", IF(COUNT(D19,E19,F19,G19)=0, "No entries!", ""))</f>
-        <v>No entries!</v>
-      </c>
-      <c r="J19" s="4">
-        <f>IF($D19=1, 3, IF($E19=1, 2, IF($F19=1, 1, IF($G19 = 1, 0, 0))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="30">
-      <c r="A20" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="21" t="str">
-        <f>IF(COUNT(D20,E20,F20,G20)=2, "More than one entry!", IF(COUNT(D20,E20,F20,G20)=0, "No entries!", ""))</f>
-        <v>No entries!</v>
-      </c>
-      <c r="J20" s="4">
-        <f>IF($D20=1, 3, IF($E20=1, 2, IF($F20=1, 1, IF($G20 = 1, 0, 0))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="21" t="str">
-        <f>IF(COUNT(D21,E21,F21,G21)=2, "More than one entry!", IF(COUNT(D21,E21,F21,G21)=0, "No entries!", ""))</f>
-        <v>No entries!</v>
-      </c>
-      <c r="J21" s="4">
-        <f>IF($D21=1, 3, IF($E21=1, 2, IF($F21=1, 1, IF($G21 = 1, 0, 0))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="21" t="str">
-        <f>IF(COUNT(D22,E22,F22,G22)=2, "More than one entry!", IF(COUNT(D22,E22,F22,G22)=0, "No entries!", ""))</f>
-        <v>No entries!</v>
-      </c>
-      <c r="J22" s="4">
-        <f>IF($D22=1, 3, IF($E22=1, 2, IF($F22=1, 1, IF($G22 = 1, 0, 0))))</f>
+      <c r="I21" s="4">
+        <f>IF($C21=1, 3, IF($D21=1, 2, IF($E21=1, 1, IF($F21 = 1, 0, 0))))</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H22">
+  <conditionalFormatting sqref="G2:G21">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(H2))&gt;0</formula>
+      <formula>LEN(TRIM(G2))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1333,38 +1303,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BDF94DC-F39D-FA47-81E6-73F58B079A6A}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.33203125" customWidth="1"/>
-    <col min="7" max="7" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.375" customWidth="1"/>
+    <col min="7" max="7" width="19.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="15.75">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1372,7 +1342,7 @@
         <v>0.3</v>
       </c>
       <c r="C2" s="4">
-        <f>SUMIF(RUBRIC!A:A, A2, RUBRIC!J:J)</f>
+        <f>SUMIF(RUBRIC!A:A, A2, RUBRIC!I:I)</f>
         <v>0</v>
       </c>
       <c r="D2" s="4">
@@ -1385,15 +1355,15 @@
       </c>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="3">
         <v>0.3</v>
       </c>
       <c r="C3" s="4">
-        <f>SUMIF(RUBRIC!A:A, A3, RUBRIC!J:J)</f>
+        <f>SUMIF(RUBRIC!A:A, A3, RUBRIC!I:I)</f>
         <v>0</v>
       </c>
       <c r="D3" s="4">
@@ -1401,15 +1371,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B4" s="3">
         <v>0.3</v>
       </c>
       <c r="C4" s="4">
-        <f>SUMIF(RUBRIC!A:A, A4, RUBRIC!J:J)</f>
+        <f>SUMIF(RUBRIC!A:A, A4, RUBRIC!I:I)</f>
         <v>0</v>
       </c>
       <c r="D4" s="4">
@@ -1417,15 +1387,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3">
         <v>0.1</v>
       </c>
       <c r="C5" s="4">
-        <f>SUMIF(RUBRIC!A:A, A5, RUBRIC!J:J)</f>
+        <f>SUMIF(RUBRIC!A:A, A5, RUBRIC!I:I)</f>
         <v>0</v>
       </c>
       <c r="D5" s="4">
@@ -1441,25 +1411,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55862989-71FD-4E9C-9096-411DB8E0B184}">
   <dimension ref="A1:O21"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.21875" customWidth="1"/>
-    <col min="2" max="2" width="108.44140625" customWidth="1"/>
-    <col min="3" max="3" width="1.44140625" customWidth="1"/>
+    <col min="1" max="1" width="19.25" customWidth="1"/>
+    <col min="2" max="2" width="108.5" customWidth="1"/>
+    <col min="3" max="3" width="1.5" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.33203125" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="1.88671875" customWidth="1"/>
-    <col min="10" max="10" width="16.88671875" customWidth="1"/>
+    <col min="5" max="5" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.375" customWidth="1"/>
+    <col min="7" max="7" width="14.625" customWidth="1"/>
+    <col min="8" max="8" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="1.875" customWidth="1"/>
+    <col min="10" max="10" width="16.875" customWidth="1"/>
     <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="2.44140625" customWidth="1"/>
-    <col min="13" max="13" width="5.109375" customWidth="1"/>
+    <col min="12" max="12" width="2.5" customWidth="1"/>
+    <col min="13" max="13" width="5.125" customWidth="1"/>
     <col min="15" max="15" width="11" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="8" customFormat="1" ht="47.25">
+    <row r="1" spans="1:15" s="8" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1468,21 +1438,21 @@
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="7"/>
       <c r="G1" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I1" s="7"/>
       <c r="J1" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K1" s="7" t="s">
         <v>5</v>
@@ -1493,23 +1463,23 @@
       </c>
       <c r="N1" s="7"/>
       <c r="O1" s="12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F2" s="13"/>
       <c r="G2" s="13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H2" s="14">
         <v>1</v>
@@ -1517,25 +1487,25 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
       <c r="K2" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M2" s="4">
         <f t="shared" ref="M2:M21" si="0">IF($E2=1, 3, IF($H2=1, 2, IF($K2 = 1, 1, 0)))</f>
         <v>2</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E3" s="14">
         <v>1</v>
@@ -1543,27 +1513,27 @@
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
       <c r="H3" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I3" s="13"/>
       <c r="J3" s="13"/>
       <c r="K3" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M3" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E4" s="14">
         <v>1</v>
@@ -1571,32 +1541,32 @@
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
       <c r="H4" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I4" s="13"/>
       <c r="J4" s="13"/>
       <c r="K4" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M4" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F5" s="13"/>
       <c r="G5" s="13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H5" s="14">
         <v>1</v>
@@ -1604,29 +1574,29 @@
       <c r="I5" s="13"/>
       <c r="J5" s="13"/>
       <c r="K5" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M5" s="4">
         <f>IF($E5=1, 3, IF($H5=1, 2, IF($K5 = 1, 1, 0)))</f>
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H6" s="15">
         <v>1</v>
@@ -1634,27 +1604,27 @@
       <c r="I6" s="13"/>
       <c r="J6" s="13"/>
       <c r="K6" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M6" s="4">
         <f>IF($E6=1, 3, IF($H6=1, 2, IF($K6 = 1, 1, 0)))</f>
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="13" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H7" s="14">
         <v>1</v>
@@ -1662,32 +1632,32 @@
       <c r="I7" s="13"/>
       <c r="J7" s="13"/>
       <c r="K7" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M7" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I8" s="13"/>
       <c r="J8" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K8" s="14">
         <v>1</v>
@@ -1697,25 +1667,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
       <c r="H9" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I9" s="13"/>
       <c r="J9" s="13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="K9" s="14">
         <v>1</v>
@@ -1725,20 +1695,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H10" s="14">
         <v>1</v>
@@ -1746,27 +1716,27 @@
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
       <c r="K10" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M10" s="4">
         <f>IF($E10=1, 3, IF($H10=1, 2, IF($K10 = 1, 1, 0)))</f>
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="13" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="H11" s="14">
         <v>1</v>
@@ -1774,30 +1744,30 @@
       <c r="I11" s="13"/>
       <c r="J11" s="13"/>
       <c r="K11" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M11" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F12" s="13"/>
       <c r="G12" s="13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H12" s="14">
         <v>1</v>
@@ -1805,27 +1775,27 @@
       <c r="I12" s="13"/>
       <c r="J12" s="13"/>
       <c r="K12" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M12" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="14" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H13" s="15">
         <v>1</v>
@@ -1838,15 +1808,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E14" s="14">
         <v>1</v>
@@ -1854,34 +1824,34 @@
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
       <c r="H14" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
       <c r="K14" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M14" s="4">
         <f>IF($E14=1, 3, IF($H14=1, 2, IF($K14 = 1, 1, 0)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F15" s="13"/>
       <c r="G15" s="13" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H15" s="15">
         <v>1</v>
@@ -1889,27 +1859,27 @@
       <c r="I15" s="13"/>
       <c r="J15" s="13"/>
       <c r="K15" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M15" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F16" s="13"/>
       <c r="G16" s="13" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H16" s="14">
         <v>1</v>
@@ -1917,27 +1887,27 @@
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
       <c r="K16" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M16" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F17" s="13"/>
       <c r="G17" s="13" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H17" s="14">
         <v>1</v>
@@ -1945,22 +1915,22 @@
       <c r="I17" s="13"/>
       <c r="J17" s="13"/>
       <c r="K17" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M17" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E18" s="14">
         <v>1</v>
@@ -1968,27 +1938,27 @@
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
       <c r="H18" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
       <c r="K18" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M18" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E19" s="14">
         <v>1</v>
@@ -1996,27 +1966,27 @@
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
       <c r="H19" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
       <c r="K19" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M19" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E20" s="14">
         <v>1</v>
@@ -2024,27 +1994,27 @@
       <c r="F20" s="13"/>
       <c r="G20" s="13"/>
       <c r="H20" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
       <c r="K20" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M20" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="B21" t="s">
-        <v>29</v>
-      </c>
       <c r="D21" s="13" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E21" s="14">
         <v>1</v>
@@ -2052,12 +2022,12 @@
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
       <c r="H21" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I21" s="13"/>
       <c r="J21" s="13"/>
       <c r="K21" s="14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M21" s="4">
         <f t="shared" si="0"/>
@@ -2072,38 +2042,38 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02ED81F7-0358-4AC1-A121-43620EA03A3D}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="15.75">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -2126,9 +2096,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3">
         <v>0.2</v>
@@ -2142,9 +2112,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B4" s="3">
         <v>0.3</v>
@@ -2158,9 +2128,9 @@
         <v>0.72222222222222221</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3">
         <v>0.1</v>
@@ -2174,9 +2144,9 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B6" s="3">
         <v>0.1</v>
@@ -2190,7 +2160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8" t="str">
         <f>IF(SUM(B2:B6) = 1, "^ sums to 1", "^ doesn't sum to 1!")</f>
         <v>^ sums to 1</v>

--- a/docs/2627/report/dapr3_2627_report_rubric.xlsx
+++ b/docs/2627/report/dapr3_2627_report_rubric.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jking34\Desktop\uoepsy_courses\dapr3\docs\2627\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F90261-3C3E-458E-9EAC-6C7725B7541A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE4927B-3A01-4B96-983B-F6EBCB22CCD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-25485" yWindow="-1110" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{80E36928-E358-2446-BA2E-DC98679EB28E}"/>
+    <workbookView xWindow="-28920" yWindow="-2805" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{80E36928-E358-2446-BA2E-DC98679EB28E}"/>
     <workbookView xWindow="-28920" yWindow="-2805" windowWidth="29040" windowHeight="15720" xr2:uid="{6478FE4C-0DDA-3A4B-B07C-63BB646B301E}"/>
   </bookViews>
   <sheets>
@@ -297,7 +297,7 @@
     <t>You introduce each figure and table in the text and cross-reference their numbers appropriately (including figures shown in the Appendix).</t>
   </si>
   <si>
-    <t>You accurately interpret the estimated quantity(ies) from your analysis to address the RQ(s)/hypothesis(es).</t>
+    <t>You accurately interpret the estimated quantity/quantities from your analysis to address each RQ/prediction.</t>
   </si>
 </sst>
 </file>
@@ -897,7 +897,7 @@
         <v>No entries!</v>
       </c>
       <c r="I2" s="4">
-        <f>IF($C2=1, 3, IF($D2=1, 2, IF($E2=1, 1, IF($F2 = 1, 0, 0))))</f>
+        <f t="shared" ref="I2:I21" si="1">IF($C2=1, 3, IF($D2=1, 2, IF($E2=1, 1, IF($F2 = 1, 0, 0))))</f>
         <v>0</v>
       </c>
     </row>
@@ -917,7 +917,7 @@
         <v>No entries!</v>
       </c>
       <c r="I3" s="4">
-        <f>IF($C3=1, 3, IF($D3=1, 2, IF($E3=1, 1, IF($F3 = 1, 0, 0))))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -937,7 +937,7 @@
         <v>No entries!</v>
       </c>
       <c r="I4" s="4">
-        <f>IF($C4=1, 3, IF($D4=1, 2, IF($E4=1, 1, IF($F4 = 1, 0, 0))))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>No entries!</v>
       </c>
       <c r="I5" s="4">
-        <f>IF($C5=1, 3, IF($D5=1, 2, IF($E5=1, 1, IF($F5 = 1, 0, 0))))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -977,7 +977,7 @@
         <v>No entries!</v>
       </c>
       <c r="I6" s="4">
-        <f>IF($C6=1, 3, IF($D6=1, 2, IF($E6=1, 1, IF($F6 = 1, 0, 0))))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M6" s="26"/>
@@ -1000,7 +1000,7 @@
         <v>No entries!</v>
       </c>
       <c r="I7" s="4">
-        <f>IF($C7=1, 3, IF($D7=1, 2, IF($E7=1, 1, IF($F7 = 1, 0, 0))))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M7" s="26"/>
@@ -1023,7 +1023,7 @@
         <v>No entries!</v>
       </c>
       <c r="I8" s="4">
-        <f>IF($C8=1, 3, IF($D8=1, 2, IF($E8=1, 1, IF($F8 = 1, 0, 0))))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M8" s="26"/>
@@ -1046,7 +1046,7 @@
         <v>No entries!</v>
       </c>
       <c r="I9" s="4">
-        <f>IF($C9=1, 3, IF($D9=1, 2, IF($E9=1, 1, IF($F9 = 1, 0, 0))))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
         <v>No entries!</v>
       </c>
       <c r="I10" s="4">
-        <f>IF($C10=1, 3, IF($D10=1, 2, IF($E10=1, 1, IF($F10 = 1, 0, 0))))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
         <v>No entries!</v>
       </c>
       <c r="I11" s="4">
-        <f>IF($C11=1, 3, IF($D11=1, 2, IF($E11=1, 1, IF($F11 = 1, 0, 0))))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
         <v>No entries!</v>
       </c>
       <c r="I12" s="4">
-        <f>IF($C12=1, 3, IF($D12=1, 2, IF($E12=1, 1, IF($F12 = 1, 0, 0))))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
         <v>No entries!</v>
       </c>
       <c r="I13" s="4">
-        <f>IF($C13=1, 3, IF($D13=1, 2, IF($E13=1, 1, IF($F13 = 1, 0, 0))))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
         <v>No entries!</v>
       </c>
       <c r="I14" s="4">
-        <f>IF($C14=1, 3, IF($D14=1, 2, IF($E14=1, 1, IF($F14 = 1, 0, 0))))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
         <v>No entries!</v>
       </c>
       <c r="I15" s="4">
-        <f>IF($C15=1, 3, IF($D15=1, 2, IF($E15=1, 1, IF($F15 = 1, 0, 0))))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
         <v>No entries!</v>
       </c>
       <c r="I16" s="4">
-        <f>IF($C16=1, 3, IF($D16=1, 2, IF($E16=1, 1, IF($F16 = 1, 0, 0))))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
         <v>No entries!</v>
       </c>
       <c r="I17" s="4">
-        <f>IF($C17=1, 3, IF($D17=1, 2, IF($E17=1, 1, IF($F17 = 1, 0, 0))))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         <v>No entries!</v>
       </c>
       <c r="I18" s="4">
-        <f>IF($C18=1, 3, IF($D18=1, 2, IF($E18=1, 1, IF($F18 = 1, 0, 0))))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
         <v>No entries!</v>
       </c>
       <c r="I19" s="4">
-        <f>IF($C19=1, 3, IF($D19=1, 2, IF($E19=1, 1, IF($F19 = 1, 0, 0))))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
         <v>No entries!</v>
       </c>
       <c r="I20" s="4">
-        <f>IF($C20=1, 3, IF($D20=1, 2, IF($E20=1, 1, IF($F20 = 1, 0, 0))))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
         <v>No entries!</v>
       </c>
       <c r="I21" s="4">
-        <f>IF($C21=1, 3, IF($D21=1, 2, IF($E21=1, 1, IF($F21 = 1, 0, 0))))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
